--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486977_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486977_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8864</v>
+        <v>1.8337</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0202</v>
+        <v>0.0456</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9066</v>
+        <v>1.788</v>
       </c>
       <c r="G2" t="n">
         <v>-1.6867</v>
@@ -610,13 +610,13 @@
         <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1767</v>
+        <v>0.124</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0272</v>
+        <v>0.0386</v>
       </c>
       <c r="U2" t="n">
-        <v>0.204</v>
+        <v>0.0854</v>
       </c>
       <c r="V2" t="n">
         <v>2.575</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9133</v>
+        <v>1.7594</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.0625</v>
+        <v>0.7572</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9758</v>
+        <v>1.0021</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7411</v>
+        <v>2.8271</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1882</v>
+        <v>0.8144</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5528999999999999</v>
+        <v>2.0128</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9558</v>
+        <v>3.2917</v>
       </c>
       <c r="K3" t="n">
-        <v>0.127</v>
+        <v>1.003</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8288</v>
+        <v>2.2886</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2147</v>
+        <v>-0.4645</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0612</v>
+        <v>-0.1887</v>
       </c>
       <c r="O3" t="n">
         <v>-0.2759</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8214</v>
+        <v>-0.616</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8847</v>
+        <v>-0.3429</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5542</v>
+        <v>-0.3722</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4389</v>
+        <v>0.0293</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1088</v>
+        <v>-0.1088</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5893</v>
+        <v>-0.1088</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8329</v>
+        <v>0.3493</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2458</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5871</v>
+        <v>1.1755</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8271</v>
+        <v>0.7411</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8144</v>
+        <v>0.1882</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0128</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2917</v>
+        <v>0.9558</v>
       </c>
       <c r="K4" t="n">
-        <v>1.003</v>
+        <v>0.127</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2886</v>
+        <v>0.8288</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4645</v>
+        <v>-0.2147</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1887</v>
+        <v>0.0612</v>
       </c>
       <c r="O4" t="n">
         <v>-0.2759</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.616</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2693</v>
+        <v>0.3207</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-0.3179</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3857</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1088</v>
+        <v>0.1088</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1088</v>
+        <v>0.5893</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>J. PARRA BAEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005</v>
+        <v>-0.1004</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8726</v>
+        <v>-0.9495</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8676</v>
+        <v>0.8491</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5582</v>
+        <v>0.3742</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7004</v>
+        <v>-0.3833</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1422</v>
+        <v>0.7575</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1676</v>
+        <v>1.0886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0492</v>
+        <v>0.1947</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1184</v>
+        <v>0.8939</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7258</v>
+        <v>-0.7144</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.578</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0238</v>
+        <v>-0.1364</v>
       </c>
       <c r="P5" t="n">
         <v>-0.4107</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>0.616</v>
+        <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5016</v>
+        <v>-0.0639</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9022</v>
+        <v>-0.225</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5994</v>
+        <v>0.161</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5277</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8295</v>
+        <v>0.2402</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3573</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PARRA BAEZ</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4898</v>
+        <v>-0.9208</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0426</v>
+        <v>1.0358</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5527</v>
+        <v>-1.9565</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3742</v>
+        <v>-0.5582</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3833</v>
+        <v>-0.7004</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7575</v>
+        <v>0.1422</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0886</v>
+        <v>0.1676</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1947</v>
+        <v>0.0492</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8939</v>
+        <v>0.1184</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7144</v>
+        <v>-0.7258</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.578</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1364</v>
+        <v>0.0238</v>
       </c>
       <c r="P6" t="n">
         <v>-0.4107</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4534</v>
+        <v>1.5759</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.318</v>
+        <v>1.0653</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1354</v>
+        <v>0.5105</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.5277</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2402</v>
+        <v>0.8295</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2402</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2393</v>
+        <v>-2.133</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1053</v>
+        <v>-1.7915</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1341</v>
+        <v>-0.3416</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1626</v>
@@ -1000,13 +1000,13 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0937</v>
+        <v>1.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0.244</v>
+        <v>0.5578</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8497</v>
+        <v>0.6423</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9384</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2489</v>
+        <v>-2.38</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8224</v>
+        <v>-1.2796</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4265</v>
+        <v>-1.1004</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5313</v>
@@ -1078,13 +1078,13 @@
         <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3563</v>
+        <v>1.2252</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1117</v>
+        <v>0.6546</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2446</v>
+        <v>0.5707</v>
       </c>
       <c r="V8" t="n">
         <v>-1.6366</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. TEJERA TEJO</t>
+          <t>G. KASANZI OBAMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.487</v>
+        <v>-3.2344</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5804</v>
+        <v>-3.2886</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9066</v>
+        <v>0.0542</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5757</v>
+        <v>-1.5765</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5312</v>
+        <v>-1.6869</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0445</v>
+        <v>0.1104</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6974</v>
+        <v>0.0513</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6974</v>
+        <v>-0.3825</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.4338</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8783</v>
+        <v>-1.6278</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8338</v>
+        <v>-1.3044</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0445</v>
+        <v>-0.3234</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2053</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.706</v>
+        <v>0.0465</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8563</v>
+        <v>-0.2597</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1504</v>
+        <v>0.3062</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. KASANZI OBAMA</t>
+          <t>J. TEJERA TEJO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0077</v>
+        <v>-3.4804</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9433</v>
+        <v>-2.5145</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0644</v>
+        <v>-0.9659</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5765</v>
+        <v>-2.5757</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6869</v>
+        <v>-1.5312</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1104</v>
+        <v>-1.0445</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0513</v>
+        <v>-0.6974</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3825</v>
+        <v>-0.6974</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4338</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6278</v>
+        <v>-1.8783</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3044</v>
+        <v>-0.8338</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3234</v>
+        <v>-1.0445</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0534</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7269</v>
+        <v>-0.6994</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9145</v>
+        <v>-0.7905</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1876</v>
+        <v>0.0911</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0396</v>
+        <v>-3.5801</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2464</v>
+        <v>-2.9054</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7932</v>
+        <v>-0.6746</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6261</v>
@@ -1312,13 +1312,13 @@
         <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0295</v>
+        <v>0.43</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1513</v>
+        <v>0.1897</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1217</v>
+        <v>0.2403</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5893</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.8747</v>
+        <v>-11.8867</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.7047</v>
+        <v>-11.7166</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1701999999999998</v>
+        <v>-0.1700999999999994</v>
       </c>
       <c r="G12" t="n">
         <v>-7.7747</v>
@@ -1381,7 +1381,7 @@
         <v>-3.234</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.160299999999999</v>
+        <v>-6.1603</v>
       </c>
       <c r="Q12" t="n">
         <v>-17.4539</v>
@@ -1390,13 +1390,13 @@
         <v>11.2939</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8279</v>
+        <v>3.8161</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4472000000000004</v>
+        <v>0.5406999999999997</v>
       </c>
       <c r="U12" t="n">
-        <v>3.2752</v>
+        <v>3.2754</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7679</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.2738</v>
+        <v>9.6774</v>
       </c>
       <c r="E13" t="n">
-        <v>5.8248</v>
+        <v>6.3478</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4491</v>
+        <v>3.3296</v>
       </c>
       <c r="G13" t="n">
         <v>7.3602</v>
@@ -1468,13 +1468,13 @@
         <v>2.6694</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2917</v>
+        <v>-0.8882</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3097</v>
+        <v>-0.7867</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.982</v>
+        <v>-0.1015</v>
       </c>
       <c r="V13" t="n">
         <v>1.7679</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. MIKHAILOV PALTARAK</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2524</v>
+        <v>4.563</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4293</v>
+        <v>4.334</v>
       </c>
       <c r="F14" t="n">
-        <v>2.823</v>
+        <v>0.229</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5789</v>
+        <v>2.4733</v>
       </c>
       <c r="H14" t="n">
-        <v>5.0414</v>
+        <v>-1.3656</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4625</v>
+        <v>3.8389</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3354</v>
+        <v>3.8804</v>
       </c>
       <c r="K14" t="n">
-        <v>4.7565</v>
+        <v>-0.4214</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4211</v>
+        <v>4.3018</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7565</v>
+        <v>-1.4071</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2849</v>
+        <v>-0.9442</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0415</v>
+        <v>-0.4629</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.616</v>
+        <v>1.6427</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.4908</v>
+        <v>-0.2053</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8748</v>
+        <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>2.119</v>
+        <v>-0.6228</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5847</v>
+        <v>-0.4108</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5343</v>
+        <v>-0.2121</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8295</v>
+        <v>1.0698</v>
       </c>
       <c r="W14" t="n">
+        <v>1.0698</v>
+      </c>
+      <c r="X14" t="n">
         <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.8295</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>M. MIKHAILOV PALTARAK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0417</v>
+        <v>2.7407</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0202</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0215</v>
+        <v>2.0436</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4733</v>
+        <v>3.5789</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3656</v>
+        <v>5.0414</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8389</v>
+        <v>-1.4625</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8804</v>
+        <v>4.3354</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4214</v>
+        <v>4.7565</v>
       </c>
       <c r="L15" t="n">
-        <v>4.3018</v>
+        <v>-0.4211</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4071</v>
+        <v>-0.7565</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9442</v>
+        <v>0.2849</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4629</v>
+        <v>-1.0415</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6427</v>
+        <v>-0.616</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2053</v>
+        <v>-3.4908</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8481</v>
+        <v>2.8748</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1441</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7246</v>
+        <v>-0.1475</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4196</v>
+        <v>0.7549</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0698</v>
+        <v>-0.8295</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0698</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5288</v>
+        <v>2.2193</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.8801</v>
+        <v>-1.5663</v>
       </c>
       <c r="F16" t="n">
-        <v>3.409</v>
+        <v>3.7856</v>
       </c>
       <c r="G16" t="n">
         <v>-1.537</v>
@@ -1702,13 +1702,13 @@
         <v>2.2588</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0081</v>
+        <v>-0.3177</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6782</v>
+        <v>-0.3644</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3299</v>
+        <v>0.0468</v>
       </c>
       <c r="V16" t="n">
         <v>2.2259</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9869</v>
+        <v>0.898</v>
       </c>
       <c r="E17" t="n">
         <v>-0.0464</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0333</v>
+        <v>0.9444</v>
       </c>
       <c r="G17" t="n">
         <v>0.5773</v>
@@ -1780,13 +1780,13 @@
         <v>0.2053</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2042</v>
+        <v>0.1153</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0659</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2701</v>
+        <v>0.1811</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8057</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0592</v>
+        <v>-1.7454</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8649</v>
+        <v>2.2721</v>
       </c>
       <c r="G18" t="n">
         <v>-1.105</v>
@@ -1858,13 +1858,13 @@
         <v>2.6694</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6355</v>
+        <v>0.3565</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8758</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5114</v>
+        <v>0.9185</v>
       </c>
       <c r="V18" t="n">
         <v>1.0698</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5022</v>
+        <v>0.3067</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2287</v>
+        <v>-1.9149</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7265</v>
+        <v>2.2217</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9296</v>
@@ -1936,13 +1936,13 @@
         <v>2.0534</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5296</v>
+        <v>-0.7206</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7905</v>
+        <v>-0.4767</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7392</v>
+        <v>-0.244</v>
       </c>
       <c r="V19" t="n">
         <v>0.1088</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. KANE</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1442</v>
+        <v>-1.0566</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.219</v>
+        <v>-0.5609</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0749</v>
+        <v>-0.4957</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2955</v>
+        <v>-0.1781</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4413</v>
+        <v>0.0323</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7368</v>
+        <v>-0.2104</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0979</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0.0584</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0395</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1977</v>
+        <v>-0.9074</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4997</v>
+        <v>-0.0261</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6974</v>
+        <v>-0.8813</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.4374</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0023</v>
+        <v>-0.6732</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2635</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2612</v>
+        <v>-0.4097</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>S. KANE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.285</v>
+        <v>-1.322</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5609</v>
+        <v>-2.219</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7241</v>
+        <v>0.897</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1781</v>
+        <v>0.2955</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0323</v>
+        <v>-0.4413</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2104</v>
+        <v>0.7368</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.0979</v>
       </c>
       <c r="K21" t="n">
         <v>0.0584</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.0395</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9074</v>
+        <v>0.1977</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0261</v>
+        <v>-0.4997</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8813</v>
+        <v>0.6974</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2053</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9016</v>
+        <v>-0.1801</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2635</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6381</v>
+        <v>0.0834</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0831</v>
+        <v>-4.981</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1098</v>
+        <v>-3.1558</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9733</v>
+        <v>-1.8251</v>
       </c>
       <c r="G22" t="n">
         <v>-2.761</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0906</v>
+        <v>0.1927</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1117</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0211</v>
+        <v>0.1271</v>
       </c>
       <c r="V22" t="n">
         <v>-3.6447</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>12.8748</v>
+        <v>13.5722</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1702000000000004</v>
+        <v>0.1701999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>12.7048</v>
+        <v>13.4022</v>
       </c>
       <c r="G23" t="n">
-        <v>7.774499999999999</v>
+        <v>7.774500000000002</v>
       </c>
       <c r="H23" t="n">
         <v>6.261100000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1.513400000000001</v>
+        <v>1.5134</v>
       </c>
       <c r="J23" t="n">
         <v>10.569</v>
@@ -2227,7 +2227,7 @@
         <v>7.3349</v>
       </c>
       <c r="L23" t="n">
-        <v>3.2339</v>
+        <v>3.233899999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-2.7941</v>
@@ -2248,13 +2248,13 @@
         <v>17.454</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.828099999999999</v>
+        <v>-2.1307</v>
       </c>
       <c r="T23" t="n">
         <v>-3.2753</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4471000000000001</v>
+        <v>1.1445</v>
       </c>
       <c r="V23" t="n">
         <v>1.768</v>
